--- a/Luban/Config/Datas/Levels/L17/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L17/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L17 W1/25; N=47; EHP=291.588000; normal:17x23,normal:18x24</t>
+          <t>L17 W1/25; N=47; EHP=724.697667; normal:17x23,normal:18x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L17 W2/25; N=53; EHP=344.299045; normal:17x27,normal:18x26</t>
+          <t>L17 W2/25; N=53; EHP=855.702961; normal:17x27,normal:18x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>3744136,3744673,3744019,3744136,3744673,3744019,3744136,3744673,3744091,3744136,3744673,3744099,3744136,3744673,3744099,3744136,3744673,3744107,3744136,3744673,3744115,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744136,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144</t>
+          <t>3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744673,3744136,3744136,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744144,3744136,3744136,3744136,3744136,3744136,3744136,3744136</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L17 W3/25; N=59; EHP=424.016102; air:2x2,air:11x1,air:12x2,air:13x1,air:14x1,normal:17x18,normal:18x18,swarm:84x16</t>
+          <t>L17 W3/25; N=59; EHP=1135.709253; normal:17x25,normal:18x18,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>3746136,3746673,3746019,3746136,3746673,3746019,3746136,3746673,3746091,3746136,3746673,3746091,3746136,3746673,3746099,3746136,3746673,3746107,3746136,3746673,3746107,3746136,3746673,3746115,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746136,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144</t>
+          <t>3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746673,3746136,3746136,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746144,3746136,3746136,3746136,3746136,3746136,3746136,3746136,3746136</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L17 W4/25; N=65; EHP=537.908514; air:2x2,air:11x2,air:12x1,air:13x2,air:14x1,normal:17x20,normal:18x19,swarm:84x18</t>
+          <t>L17 W4/25; N=65; EHP=1445.219811; normal:17x28,normal:18x19,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3748136,3748673,3748019,3748668,3748136,3748673,3748091,3748668,3748136,3748673,3748091,3748668,3748136,3748673,3748099,3748868,3748136,3748673,3748099,3748868,3748136,3748673,3748107,3748868,3748136,3748673,3748107,3748988,3748136,3748673,3748115,3748988,3748136,3748673,3748115,3748988,3748136,3748673,3748988,3748136,3748673,3748136,3748673,3748136,3748673,3748136,3748673,3748136,3748673,3748136,3748673,3748144,3748673,3748144,3748673,3748144,3748673,3748144,3748144,3748144,3748144,3748144,3748144,3748144,3748144,3748144,3748144,3748144,3748144,3748144,3748144</t>
+          <t>3748136,3748019,3748019,3748668,3748136,3748091,3748091,3748668,3748136,3748091,3748091,3748668,3748136,3748099,3748099,3748868,3748136,3748099,3748099,3748868,3748136,3748107,3748107,3748868,3748136,3748107,3748107,3748988,3748136,3748115,3748115,3748988,3748136,3748115,3748115,3748988,3748136,3748673,3748988,3748136,3748673,3748136,3748673,3748136,3748673,3748136,3748673,3748136,3748673,3748136,3748673,3748144,3748673,3748144,3748673,3748144,3748673,3748144,3748144,3748144,3748144,3748144,3748144,3748144,3748144,3748144,3748144,3748144,3748144,3748144,3748144</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L17 W5/25; N=71; EHP=1011.992609; air:2x1,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x16,normal:18x17,medium:83x3,swarm:84x19,medium:108x3,medium:123x4</t>
+          <t>L17 W5/25; N=71; EHP=2549.244797; air:2x2,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x3,medium:108x3,medium:123x4,normal:17x16,normal:18x17,swarm:84x10 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3750136,3750673,3750242,3750019,3750668,3750136,3750673,3750242,3750019,3750668,3750136,3750673,3750466,3750091,3750668,3750136,3750673,3750466,3750091,3750668,3750136,3750673,3750514,3750099,3750868,3750136,3750673,3750514,3750099,3750868,3750136,3750673,3750514,3750107,3750868,3750136,3750673,3750786,3750115,3750868,3750136,3750673,3750786,3750115,3750988,3750136,3750673,3750988,3750136,3750673,3750988,3750136,3750673,3750136,3750673,3750136,3750673,3750144,3750673,3750144,3750673,3750144,3750673,3750144,3750673,3750144,3750673,3750144,3750673,3750144,3750673,3750144,3750144,3750144,3750144,3750144,3750144</t>
+          <t>3750136,3750019,3750242,3750019,3750668,3750136,3750019,3750242,3750019,3750668,3750136,3750091,3750466,3750091,3750668,3750136,3750091,3750466,3750091,3750668,3750136,3750099,3750514,3750099,3750868,3750136,3750099,3750514,3750099,3750868,3750136,3750107,3750514,3750107,3750868,3750136,3750115,3750786,3750115,3750868,3750136,3750115,3750786,3750115,3750988,3750136,3750673,3750988,3750136,3750673,3750988,3750136,3750673,3750136,3750673,3750136,3750673,3750144,3750673,3750144,3750673,3750144,3750673,3750144,3750673,3750144,3750673,3750144,3750673,3750144,3750673,3750144,3750144,3750144,3750144,3750144,3750144</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L17 W6/25; N=77; EHP=1033.000000; air:2x2,air:11x2,air:12x2,air:13x1,air:14x2,normal:17x14,normal:18x13,fast:30x2,fast:58x2,fast:64x3,medium:83x4,swarm:84x21,fast:98x2,medium:108x4,medium:123x3</t>
+          <t>L17 W6/25; N=77; EHP=2599.885691; air:2x4,air:11x4,air:12x4,air:13x2,air:14x4,fast:30x2,fast:58x2,fast:64x3,fast:98x2,medium:83x4,medium:108x4,medium:123x3,normal:17x14,normal:18x13,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3752136,3752673,3752242,3752019,3752668,3752136,3752673,3752242,3752019,3752668,3752136,3752673,3752242,3752091,3752668,3752136,3752673,3752466,3752091,3752668,3752136,3752673,3752466,3752099,3752868,3752136,3752673,3752514,3752099,3752868,3752136,3752673,3752514,3752107,3752868,3752136,3752673,3752786,3752107,3752868,3752136,3752673,3752786,3752115,3752988,3752136,3752673,3752115,3752988,3752136,3752673,3752988,3752136,3752673,3752988,3752136,3752673,3752136,3752673,3752144,3752673,3752144,3752673,3752144,3752673,3752144,3752673,3752144,3752673,3752144,3752673,3752144,3752673,3752144,3752673,3752144,3752673,3752144,3752144,3752144,3752144,3752144,3752144</t>
+          <t>3752136,3752019,3752242,3752019,3752668,3752136,3752019,3752242,3752019,3752668,3752136,3752091,3752242,3752091,3752668,3752136,3752091,3752466,3752091,3752668,3752136,3752099,3752466,3752099,3752868,3752136,3752099,3752514,3752099,3752868,3752136,3752107,3752514,3752107,3752868,3752136,3752107,3752786,3752107,3752868,3752136,3752115,3752786,3752115,3752988,3752136,3752115,3752115,3752988,3752136,3752673,3752988,3752136,3752673,3752988,3752136,3752673,3752136,3752673,3752144,3752673,3752144,3752673,3752144,3752673,3752144,3752673,3752144,3752673,3752144,3752673,3752144,3752673,3752144,3752673,3752144,3752673,3752144,3752144,3752144,3752144,3752144,3752144</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L17 W7/25; N=83; EHP=1160.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x14,normal:18x15,fast:30x3,fast:58x2,fast:64x2,medium:83x4,swarm:84x23,fast:98x2,medium:108x4,medium:123x4</t>
+          <t>L17 W7/25; N=83; EHP=2920.690061; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x2,fast:98x2,medium:83x4,medium:108x4,medium:123x4,normal:17x14,normal:18x15,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3754136,3754673,3754242,3754019,3754668,3754136,3754673,3754242,3754019,3754668,3754136,3754673,3754466,3754091,3754668,3754136,3754673,3754466,3754091,3754668,3754136,3754673,3754466,3754099,3754868,3754136,3754673,3754514,3754099,3754868,3754136,3754673,3754514,3754099,3754868,3754136,3754673,3754786,3754107,3754868,3754136,3754673,3754786,3754107,3754988,3754136,3754673,3754786,3754115,3754988,3754136,3754673,3754115,3754988,3754136,3754673,3754988,3754136,3754673,3754988,3754136,3754673,3754136,3754673,3754136,3754673,3754144,3754673,3754144,3754673,3754144,3754673,3754144,3754673,3754144,3754673,3754144,3754673,3754144,3754673,3754144,3754673,3754144,3754144,3754144,3754144,3754144,3754144,3754144</t>
+          <t>3754136,3754019,3754242,3754019,3754668,3754136,3754019,3754242,3754019,3754668,3754136,3754091,3754466,3754091,3754668,3754136,3754091,3754466,3754091,3754668,3754136,3754099,3754466,3754099,3754868,3754136,3754099,3754514,3754099,3754868,3754136,3754099,3754514,3754099,3754868,3754136,3754107,3754786,3754107,3754868,3754136,3754107,3754786,3754107,3754988,3754136,3754115,3754786,3754115,3754988,3754136,3754115,3754115,3754988,3754136,3754673,3754988,3754136,3754673,3754988,3754136,3754673,3754136,3754673,3754136,3754673,3754144,3754673,3754144,3754673,3754144,3754673,3754144,3754673,3754144,3754673,3754144,3754673,3754144,3754673,3754144,3754673,3754144,3754144,3754144,3754144,3754144,3754144,3754144</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L17 W8/25; N=89; EHP=1492.000000; air:2x2,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x16,normal:18x15,fast:30x2,fast:58x3,fast:64x2,medium:83x4,swarm:84x24,fast:98x3,medium:108x4,medium:123x5</t>
+          <t>L17 W8/25; N=89; EHP=3757.791795; air:2x4,air:11x4,air:12x6,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x2,fast:98x3,medium:83x4,medium:108x4,medium:123x5,normal:17x16,normal:18x15,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3756136,3756673,3756242,3756019,3756668,3756136,3756673,3756242,3756019,3756668,3756136,3756673,3756242,3756019,3756668,3756136,3756673,3756466,3756091,3756668,3756136,3756673,3756466,3756091,3756668,3756136,3756673,3756466,3756099,3756868,3756136,3756673,3756514,3756099,3756868,3756136,3756673,3756514,3756107,3756868,3756136,3756673,3756514,3756107,3756868,3756136,3756673,3756786,3756115,3756868,3756136,3756673,3756786,3756115,3756988,3756136,3756673,3756988,3756136,3756673,3756988,3756136,3756673,3756988,3756136,3756673,3756136,3756673,3756144,3756673,3756144,3756673,3756144,3756673,3756144,3756673,3756144,3756673,3756144,3756673,3756144,3756673,3756144,3756673,3756144,3756673,3756144,3756673,3756144,3756144,3756144,3756144,3756144,3756144,3756144</t>
+          <t>3756136,3756019,3756242,3756019,3756668,3756136,3756019,3756242,3756019,3756668,3756136,3756019,3756242,3756019,3756668,3756136,3756091,3756466,3756091,3756668,3756136,3756091,3756466,3756091,3756668,3756136,3756099,3756466,3756099,3756868,3756136,3756099,3756514,3756099,3756868,3756136,3756107,3756514,3756107,3756868,3756136,3756107,3756514,3756107,3756868,3756136,3756115,3756786,3756115,3756868,3756136,3756115,3756786,3756115,3756988,3756136,3756673,3756988,3756136,3756673,3756988,3756136,3756673,3756988,3756136,3756673,3756136,3756673,3756144,3756673,3756144,3756673,3756144,3756673,3756144,3756673,3756144,3756673,3756144,3756673,3756144,3756673,3756144,3756673,3756144,3756673,3756144,3756673,3756144,3756144,3756144,3756144,3756144,3756144,3756144</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L17 W9/25; N=95; EHP=1904.000000; air:2x3,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x16,normal:18x17,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x26,fast:98x2,medium:108x5,medium:123x4</t>
+          <t>L17 W9/25; N=95; EHP=4791.253971; air:2x6,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x2,medium:83x5,medium:108x5,medium:123x4,normal:17x16,normal:18x17,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3758136,3758673,3758242,3758019,3758668,3758136,3758673,3758242,3758019,3758668,3758136,3758673,3758242,3758091,3758668,3758136,3758673,3758466,3758091,3758668,3758136,3758673,3758466,3758091,3758668,3758136,3758673,3758466,3758099,3758868,3758136,3758673,3758514,3758099,3758868,3758136,3758673,3758514,3758107,3758868,3758136,3758673,3758514,3758107,3758868,3758136,3758673,3758786,3758107,3758868,3758136,3758673,3758786,3758115,3758988,3758136,3758673,3758786,3758115,3758988,3758136,3758673,3758988,3758136,3758673,3758988,3758136,3758673,3758988,3758136,3758673,3758136,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758144,3758144,3758144,3758144,3758144</t>
+          <t>3758136,3758019,3758242,3758019,3758668,3758136,3758019,3758242,3758019,3758668,3758136,3758091,3758242,3758091,3758668,3758136,3758091,3758466,3758091,3758668,3758136,3758091,3758466,3758091,3758668,3758136,3758099,3758466,3758099,3758868,3758136,3758099,3758514,3758099,3758868,3758136,3758107,3758514,3758107,3758868,3758136,3758107,3758514,3758107,3758868,3758136,3758107,3758786,3758107,3758868,3758136,3758115,3758786,3758115,3758988,3758136,3758115,3758786,3758115,3758988,3758136,3758673,3758988,3758136,3758673,3758988,3758136,3758673,3758988,3758136,3758673,3758136,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758673,3758144,3758144,3758144,3758144,3758144,3758144</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L17 W10/25; N=101; EHP=3511.000000; air:2x2,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x17,normal:18x17,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x28,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L17 W10/25; N=101; EHP=8838.289248; air:2x4,air:11x6,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x5,normal:17x17,normal:18x17,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3760136,3760673,3760242,3760019,3760668,3760253,3760136,3760673,3760242,3760019,3760668,3760325,3760136,3760673,3760242,3760091,3760668,3760325,3760136,3760673,3760466,3760091,3760668,3760541,3760136,3760673,3760466,3760091,3760668,3760565,3760136,3760673,3760466,3760099,3760868,3760645,3760136,3760673,3760514,3760099,3760868,3760693,3760136,3760673,3760514,3760099,3760868,3760709,3760136,3760673,3760514,3760107,3760868,3761021,3760136,3760673,3760786,3760107,3760868,3761021,3760136,3760673,3760786,3760115,3760988,3760136,3760673,3760786,3760115,3760988,3760136,3760673,3760115,3760988,3760144,3760673,3760988,3760144,3760673,3760988,3760144,3760673,3760988,3760144,3760673,3760144,3760673,3760144,3760673,3760144,3760673,3760144,3760673,3760144,3760673,3760144,3760673,3760144,3760673,3760144,3760673,3760144,3760673,3760144,3760673,3760673,3760673</t>
+          <t>3760136,3760019,3760242,3760019,3760668,3760253,3760136,3760019,3760242,3760019,3760668,3760325,3760136,3760091,3760242,3760091,3760668,3760325,3760136,3760091,3760466,3760091,3760668,3760541,3760136,3760091,3760466,3760091,3760668,3760565,3760136,3760099,3760466,3760099,3760868,3760645,3760136,3760099,3760514,3760099,3760868,3760693,3760136,3760099,3760514,3760099,3760868,3760709,3760136,3760107,3760514,3760107,3760868,3761021,3760136,3760107,3760786,3760107,3760868,3761021,3760136,3760115,3760786,3760115,3760988,3760136,3760115,3760786,3760115,3760988,3760136,3760115,3760115,3760988,3760144,3760673,3760988,3760144,3760673,3760988,3760144,3760673,3760988,3760144,3760673,3760144,3760673,3760144,3760673,3760144,3760673,3760144,3760673,3760144,3760673,3760144,3760673,3760144,3760673,3760144,3760673,3760144,3760673,3760144,3760673,3760673,3760673</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L17 W11/25; N=107; EHP=3582.000000; air:2x2,air:11x3,air:12x3,air:13x2,air:14x3,normal:17x13,normal:18x14,fast:30x3,heavy:31x1,heavy:40x2,fast:58x3,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x5,swarm:84x29,heavy:86x1,heavy:88x1,fast:98x3,medium:108x5,medium:123x6,heavy:127x2</t>
+          <t>L17 W11/25; N=107; EHP=9006.686577; air:2x4,air:11x6,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x3,heavy:31x1,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x5,medium:108x5,medium:123x6,normal:17x13,normal:18x14,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3762136,3762673,3762242,3762019,3762668,3762253,3762136,3762673,3762242,3762019,3762668,3762325,3762136,3762673,3762242,3762019,3762668,3762541,3762136,3762673,3762466,3762091,3762668,3762541,3762136,3762673,3762466,3762091,3762668,3762565,3762136,3762673,3762466,3762099,3762868,3762565,3762136,3762673,3762514,3762099,3762868,3762645,3762136,3762673,3762514,3762099,3762868,3762693,3762136,3762673,3762514,3762107,3762868,3762709,3762136,3762673,3762786,3762107,3762868,3763021,3762136,3762673,3762786,3762107,3762868,3763021,3762136,3762673,3762786,3762115,3762988,3762136,3762673,3762786,3762115,3762988,3762136,3762673,3762115,3762988,3762144,3762673,3762988,3762144,3762673,3762988,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762673,3762673,3762673</t>
+          <t>3762136,3762019,3762242,3762019,3762668,3762253,3762136,3762019,3762242,3762019,3762668,3762325,3762136,3762019,3762242,3762019,3762668,3762541,3762136,3762091,3762466,3762091,3762668,3762541,3762136,3762091,3762466,3762091,3762668,3762565,3762136,3762099,3762466,3762099,3762868,3762565,3762136,3762099,3762514,3762099,3762868,3762645,3762136,3762099,3762514,3762099,3762868,3762693,3762136,3762107,3762514,3762107,3762868,3762709,3762136,3762107,3762786,3762107,3762868,3763021,3762136,3762107,3762786,3762107,3762868,3763021,3762136,3762115,3762786,3762115,3762988,3762136,3762115,3762786,3762115,3762988,3762136,3762115,3762115,3762988,3762144,3762673,3762988,3762144,3762673,3762988,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762144,3762673,3762673,3762673,3762673</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L17 W12/25; N=113; EHP=3707.000000; air:2x3,air:11x2,air:12x3,air:13x3,air:14x3,normal:17x14,normal:18x14,fast:30x3,heavy:31x1,heavy:40x1,fast:58x3,fast:64x3,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x5,swarm:84x31,heavy:86x1,heavy:88x1,fast:98x4,medium:108x6,medium:123x5,heavy:127x2</t>
+          <t>L17 W12/25; N=113; EHP=9323.522769; air:2x6,air:11x4,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x5,medium:108x6,medium:123x5,normal:17x14,normal:18x14,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3764136,3764673,3764242,3764019,3764668,3764253,3764136,3764673,3764242,3764019,3764668,3764325,3764136,3764673,3764242,3764019,3764668,3764541,3764136,3764673,3764466,3764091,3764668,3764541,3764136,3764673,3764466,3764091,3764668,3764565,3764136,3764673,3764466,3764091,3764668,3764565,3764136,3764673,3764466,3764099,3764868,3764645,3764136,3764673,3764514,3764099,3764868,3764693,3764136,3764673,3764514,3764099,3764868,3764709,3764136,3764673,3764514,3764107,3764868,3764709,3764136,3764673,3764514,3764107,3764868,3765021,3764136,3764673,3764786,3764107,3764988,3764136,3764673,3764786,3764115,3764988,3764136,3764673,3764786,3764115,3764988,3764136,3764673,3764988,3764144,3764673,3764988,3764144,3764673,3764988,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764673,3764673,3764673</t>
+          <t>3764136,3764019,3764242,3764019,3764668,3764253,3764136,3764019,3764242,3764019,3764668,3764325,3764136,3764019,3764242,3764019,3764668,3764541,3764136,3764091,3764466,3764091,3764668,3764541,3764136,3764091,3764466,3764091,3764668,3764565,3764136,3764091,3764466,3764091,3764668,3764565,3764136,3764099,3764466,3764099,3764868,3764645,3764136,3764099,3764514,3764099,3764868,3764693,3764136,3764099,3764514,3764099,3764868,3764709,3764136,3764107,3764514,3764107,3764868,3764709,3764136,3764107,3764514,3764107,3764868,3765021,3764136,3764107,3764786,3764107,3764988,3764136,3764115,3764786,3764115,3764988,3764136,3764115,3764786,3764115,3764988,3764136,3764673,3764988,3764144,3764673,3764988,3764144,3764673,3764988,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764144,3764673,3764673,3764673,3764673</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L17 W13/25; N=119; EHP=4522.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x2,normal:17x15,normal:18x15,fast:30x3,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x33,heavy:86x1,heavy:88x2,fast:98x3,medium:108x5,medium:123x6,heavy:127x1</t>
+          <t>L17 W13/25; N=119; EHP=11366.925075; air:2x6,air:11x6,air:12x6,air:13x6,air:14x4,fast:30x3,fast:58x4,fast:64x4,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x1,medium:83x6,medium:108x5,medium:123x6,normal:17x15,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3766136,3766673,3766242,3766019,3766668,3766253,3766136,3766673,3766242,3766019,3766668,3766325,3766136,3766673,3766242,3766019,3766668,3766541,3766136,3766673,3766242,3766091,3766668,3766541,3766136,3766673,3766466,3766091,3766668,3766565,3766136,3766673,3766466,3766091,3766668,3766645,3766136,3766673,3766466,3766099,3766868,3766645,3766136,3766673,3766514,3766099,3766868,3766693,3766136,3766673,3766514,3766099,3766868,3766693,3766136,3766673,3766514,3766107,3766868,3766709,3766136,3766673,3766514,3766107,3766868,3766709,3766136,3766673,3766786,3766107,3766868,3767021,3766136,3766673,3766786,3766115,3766988,3766136,3766673,3766786,3766115,3766988,3766136,3766673,3766786,3766115,3766988,3766144,3766673,3766988,3766144,3766673,3766988,3766144,3766673,3766988,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766673,3766673,3766673,3766673,3766673</t>
+          <t>3766136,3766019,3766242,3766019,3766668,3766253,3766136,3766019,3766242,3766019,3766668,3766325,3766136,3766019,3766242,3766019,3766668,3766541,3766136,3766091,3766242,3766091,3766668,3766541,3766136,3766091,3766466,3766091,3766668,3766565,3766136,3766091,3766466,3766091,3766668,3766645,3766136,3766099,3766466,3766099,3766868,3766645,3766136,3766099,3766514,3766099,3766868,3766693,3766136,3766099,3766514,3766099,3766868,3766693,3766136,3766107,3766514,3766107,3766868,3766709,3766136,3766107,3766514,3766107,3766868,3766709,3766136,3766107,3766786,3766107,3766868,3767021,3766136,3766115,3766786,3766115,3766988,3766136,3766115,3766786,3766115,3766988,3766136,3766115,3766786,3766115,3766988,3766144,3766673,3766988,3766144,3766673,3766988,3766144,3766673,3766988,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766144,3766673,3766673,3766673,3766673,3766673,3766673</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L17 W14/25; N=125; EHP=5455.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x15,fast:30x4,heavy:31x1,heavy:40x1,fast:58x3,fast:64x4,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x35,heavy:86x2,heavy:88x2,fast:98x4,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L17 W14/25; N=125; EHP=13714.914892; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x4,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x15,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3768136,3768673,3768242,3768019,3768668,3768253,3768542,3768136,3768673,3768242,3768019,3768668,3768253,3768136,3768673,3768242,3768019,3768668,3768325,3768136,3768673,3768242,3768091,3768668,3768325,3768136,3768673,3768466,3768091,3768668,3768541,3768136,3768673,3768466,3768091,3768668,3768565,3768136,3768673,3768466,3768099,3768868,3768645,3768136,3768673,3768466,3768099,3768868,3768645,3768136,3768673,3768514,3768099,3768868,3768693,3768136,3768673,3768514,3768107,3768868,3768693,3768136,3768673,3768514,3768107,3768868,3768709,3768136,3768673,3768786,3768107,3768868,3768709,3768136,3768673,3768786,3768107,3768868,3769021,3768136,3768673,3768786,3768115,3768988,3768136,3768673,3768786,3768115,3768988,3768144,3768673,3768115,3768988,3768144,3768673,3768988,3768144,3768673,3768988,3768144,3768673,3768988,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768673,3768673,3768673,3768673,3768673</t>
+          <t>3768136,3768019,3768242,3768019,3768668,3768253,3768542,3768136,3768019,3768242,3768019,3768668,3768253,3768136,3768019,3768242,3768019,3768668,3768325,3768136,3768091,3768242,3768091,3768668,3768325,3768136,3768091,3768466,3768091,3768668,3768541,3768136,3768091,3768466,3768091,3768668,3768565,3768136,3768099,3768466,3768099,3768868,3768645,3768136,3768099,3768466,3768099,3768868,3768645,3768136,3768099,3768514,3768099,3768868,3768693,3768136,3768107,3768514,3768107,3768868,3768693,3768136,3768107,3768514,3768107,3768868,3768709,3768136,3768107,3768786,3768107,3768868,3768709,3768136,3768107,3768786,3768107,3768868,3769021,3768136,3768115,3768786,3768115,3768988,3768136,3768115,3768786,3768115,3768988,3768144,3768115,3768115,3768988,3768144,3768673,3768988,3768144,3768673,3768988,3768144,3768673,3768988,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768144,3768673,3768673,3768673,3768673,3768673,3768673</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L17 W15/25; N=131; EHP=9522.000000; air:2x3,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x15,normal:18x16,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x3,elite:67x1,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x36,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x6,heavy:127x1</t>
+          <t>L17 W15/25; N=131; EHP=23935.850248; air:2x6,air:11x6,air:12x6,air:13x8,air:14x6,elite:67x1,fast:30x4,fast:58x4,fast:64x3,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x6,medium:108x7,medium:123x6,normal:17x15,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3770136,3770673,3770242,3770019,3770668,3770253,3770136,3770673,3770242,3770019,3770668,3770253,3770136,3770673,3770242,3770019,3770668,3770325,3770136,3770673,3770242,3770091,3770668,3770325,3770136,3770673,3770466,3770091,3770668,3770541,3770136,3770673,3770466,3770091,3770668,3770565,3770136,3770673,3770466,3770091,3770668,3770645,3770136,3770673,3770466,3770099,3770868,3770645,3770136,3770673,3770514,3770099,3770868,3770693,3770136,3770673,3770514,3770099,3770868,3770693,3770136,3770673,3770514,3770107,3770868,3770709,3770136,3770673,3770514,3770107,3770868,3771021,3770136,3770673,3770786,3770107,3770868,3771021,3770136,3770673,3770786,3770115,3770988,3770136,3770673,3770786,3770115,3770988,3770136,3770673,3770786,3770115,3770988,3770136,3770673,3770988,3770144,3770673,3770988,3770144,3770673,3770988,3770144,3770673,3770988,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770673,3770673,3770673,3770673</t>
+          <t>3770136,3770019,3770242,3770019,3770668,3770253,3770136,3770019,3770242,3770019,3770668,3770253,3770136,3770019,3770242,3770019,3770668,3770325,3770136,3770091,3770242,3770091,3770668,3770325,3770136,3770091,3770466,3770091,3770668,3770541,3770136,3770091,3770466,3770091,3770668,3770565,3770136,3770091,3770466,3770091,3770668,3770645,3770136,3770099,3770466,3770099,3770868,3770645,3770136,3770099,3770514,3770099,3770868,3770693,3770136,3770099,3770514,3770099,3770868,3770693,3770136,3770107,3770514,3770107,3770868,3770709,3770136,3770107,3770514,3770107,3770868,3771021,3770136,3770107,3770786,3770107,3770868,3771021,3770136,3770115,3770786,3770115,3770988,3770136,3770115,3770786,3770115,3770988,3770136,3770115,3770786,3770115,3770988,3770136,3770673,3770988,3770144,3770673,3770988,3770144,3770673,3770988,3770144,3770673,3770988,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770144,3770673,3770673,3770673,3770673,3770673</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L17 W16/25; N=137; EHP=9713.000000; air:2x3,air:11x4,air:12x3,air:13x3,air:14x3,normal:17x17,normal:18x17,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x7,swarm:84x38,heavy:86x2,heavy:88x1,fast:98x4,medium:108x6,medium:123x7,heavy:127x2</t>
+          <t>L17 W16/25; N=137; EHP=24411.996284; air:2x6,air:11x8,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x7,medium:108x6,medium:123x7,normal:17x17,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3772136,3772673,3772242,3772019,3772668,3772253,3772136,3772673,3772242,3772019,3772668,3772253,3772136,3772673,3772242,3772019,3772668,3772325,3772136,3772673,3772242,3772091,3772668,3772325,3772136,3772673,3772466,3772091,3772668,3772541,3772136,3772673,3772466,3772091,3772668,3772541,3772136,3772673,3772466,3772099,3772668,3772565,3772136,3772673,3772466,3772099,3772868,3772565,3772136,3772673,3772466,3772099,3772868,3772645,3772136,3772673,3772514,3772099,3772868,3772693,3772136,3772673,3772514,3772107,3772868,3772693,3772136,3772673,3772514,3772107,3772868,3772709,3772136,3772673,3772514,3772107,3772868,3773021,3772136,3772673,3772786,3772115,3772868,3773021,3772136,3772673,3772786,3772115,3772988,3772136,3772673,3772786,3772115,3772988,3772136,3772673,3772786,3772115,3772988,3772144,3772673,3772988,3772144,3772673,3772988,3772144,3772673,3772988,3772144,3772673,3772988,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772673,3772673,3772673,3772673,3772673,3772673</t>
+          <t>3772136,3772019,3772242,3772019,3772668,3772253,3772136,3772019,3772242,3772019,3772668,3772253,3772136,3772019,3772242,3772019,3772668,3772325,3772136,3772091,3772242,3772091,3772668,3772325,3772136,3772091,3772466,3772091,3772668,3772541,3772136,3772091,3772466,3772091,3772668,3772541,3772136,3772099,3772466,3772099,3772668,3772565,3772136,3772099,3772466,3772099,3772868,3772565,3772136,3772099,3772466,3772099,3772868,3772645,3772136,3772099,3772514,3772099,3772868,3772693,3772136,3772107,3772514,3772107,3772868,3772693,3772136,3772107,3772514,3772107,3772868,3772709,3772136,3772107,3772514,3772107,3772868,3773021,3772136,3772115,3772786,3772115,3772868,3773021,3772136,3772115,3772786,3772115,3772988,3772136,3772115,3772786,3772115,3772988,3772136,3772115,3772786,3772115,3772988,3772144,3772673,3772988,3772144,3772673,3772988,3772144,3772673,3772988,3772144,3772673,3772988,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772144,3772673,3772673,3772673,3772673,3772673,3772673,3772673</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L17 W17/25; N=143; EHP=9908.000000; air:2x3,air:11x3,air:12x4,air:13x3,air:14x4,normal:17x17,normal:18x17,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x40,heavy:86x2,heavy:88x1,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L17 W17/25; N=143; EHP=24906.539168; air:2x6,air:11x6,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x5,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x17,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3774136,3774673,3774242,3774019,3774668,3774253,3774136,3774673,3774242,3774019,3774668,3774253,3774136,3774673,3774242,3774019,3774668,3774325,3774136,3774673,3774242,3774019,3774668,3774325,3774136,3774673,3774466,3774091,3774668,3774541,3774136,3774673,3774466,3774091,3774668,3774541,3774136,3774673,3774466,3774091,3774668,3774565,3774136,3774673,3774466,3774099,3774868,3774565,3774136,3774673,3774514,3774099,3774868,3774645,3774136,3774673,3774514,3774099,3774868,3774693,3774136,3774673,3774514,3774099,3774868,3774709,3774136,3774673,3774514,3774107,3774868,3774709,3774136,3774673,3774514,3774107,3774868,3775021,3774136,3774673,3774786,3774107,3774868,3775021,3774136,3774673,3774786,3774107,3774868,3774136,3774673,3774786,3774115,3774988,3774136,3774673,3774786,3774115,3774988,3774136,3774673,3774115,3774988,3774136,3774673,3774988,3774144,3774673,3774988,3774144,3774673,3774988,3774144,3774673,3774988,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774673,3774673,3774673,3774673</t>
+          <t>3774136,3774019,3774242,3774019,3774668,3774253,3774136,3774019,3774242,3774019,3774668,3774253,3774136,3774019,3774242,3774019,3774668,3774325,3774136,3774019,3774242,3774019,3774668,3774325,3774136,3774091,3774466,3774091,3774668,3774541,3774136,3774091,3774466,3774091,3774668,3774541,3774136,3774091,3774466,3774091,3774668,3774565,3774136,3774099,3774466,3774099,3774868,3774565,3774136,3774099,3774514,3774099,3774868,3774645,3774136,3774099,3774514,3774099,3774868,3774693,3774136,3774099,3774514,3774099,3774868,3774709,3774136,3774107,3774514,3774107,3774868,3774709,3774136,3774107,3774514,3774107,3774868,3775021,3774136,3774107,3774786,3774107,3774868,3775021,3774136,3774107,3774786,3774107,3774868,3774136,3774115,3774786,3774115,3774988,3774136,3774115,3774786,3774115,3774988,3774136,3774115,3774115,3774988,3774136,3774673,3774988,3774144,3774673,3774988,3774144,3774673,3774988,3774144,3774673,3774988,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774144,3774673,3774673,3774673,3774673,3774673</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L17 W18/25; N=149; EHP=10586.000000; air:2x4,air:11x3,air:12x4,air:13x4,air:14x3,normal:17x19,normal:18x18,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x41,heavy:86x1,heavy:88x2,fast:98x4,medium:108x8,medium:123x7,heavy:127x2</t>
+          <t>L17 W18/25; N=149; EHP=26616.616024; air:2x8,air:11x6,air:12x8,air:13x8,air:14x6,fast:30x4,fast:58x4,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x7,medium:108x8,medium:123x7,normal:17x19,normal:18x18,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3776136,3776673,3776242,3776019,3776668,3776253,3776136,3776673,3776242,3776019,3776668,3776325,3776136,3776673,3776242,3776019,3776668,3776325,3776136,3776673,3776242,3776019,3776668,3776541,3776136,3776673,3776242,3776091,3776668,3776541,3776136,3776673,3776466,3776091,3776668,3776565,3776136,3776673,3776466,3776091,3776668,3776565,3776136,3776673,3776466,3776091,3776668,3776645,3776136,3776673,3776466,3776099,3776868,3776645,3776136,3776673,3776514,3776099,3776868,3776693,3776136,3776673,3776514,3776099,3776868,3776693,3776136,3776673,3776514,3776107,3776868,3776709,3776136,3776673,3776514,3776107,3776868,3776709,3776136,3776673,3776786,3776107,3776868,3777021,3776136,3776673,3776786,3776107,3776868,3777021,3776136,3776673,3776786,3776115,3776988,3776136,3776673,3776786,3776115,3776988,3776136,3776673,3776786,3776115,3776988,3776144,3776673,3776115,3776988,3776144,3776673,3776988,3776144,3776673,3776988,3776144,3776673,3776988,3776144,3776673,3776988,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776673,3776673,3776673,3776673,3776673,3776673</t>
+          <t>3776136,3776019,3776242,3776019,3776668,3776253,3776136,3776019,3776242,3776019,3776668,3776325,3776136,3776019,3776242,3776019,3776668,3776325,3776136,3776019,3776242,3776019,3776668,3776541,3776136,3776091,3776242,3776091,3776668,3776541,3776136,3776091,3776466,3776091,3776668,3776565,3776136,3776091,3776466,3776091,3776668,3776565,3776136,3776091,3776466,3776091,3776668,3776645,3776136,3776099,3776466,3776099,3776868,3776645,3776136,3776099,3776514,3776099,3776868,3776693,3776136,3776099,3776514,3776099,3776868,3776693,3776136,3776107,3776514,3776107,3776868,3776709,3776136,3776107,3776514,3776107,3776868,3776709,3776136,3776107,3776786,3776107,3776868,3777021,3776136,3776107,3776786,3776107,3776868,3777021,3776136,3776115,3776786,3776115,3776988,3776136,3776115,3776786,3776115,3776988,3776136,3776115,3776786,3776115,3776988,3776144,3776115,3776115,3776988,3776144,3776673,3776988,3776144,3776673,3776988,3776144,3776673,3776988,3776144,3776673,3776988,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776144,3776673,3776673,3776673,3776673,3776673,3776673,3776673</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L17 W19/25; N=155; EHP=12261.000000; air:2x4,air:11x4,air:12x3,air:13x4,air:14x4,normal:17x18,normal:18x19,fast:30x5,heavy:31x1,heavy:40x2,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x43,heavy:86x2,heavy:88x2,fast:98x5,medium:108x7,medium:123x8,heavy:127x2</t>
+          <t>L17 W19/25; N=155; EHP=30832.693457; air:2x8,air:11x8,air:12x6,air:13x8,air:14x8,fast:30x5,fast:58x4,fast:64x4,fast:98x5,heavy:31x1,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x7,medium:123x8,normal:17x18,normal:18x19,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3778136,3778673,3778242,3778019,3778668,3778253,3778542,3778136,3778673,3778242,3778019,3778668,3778253,3778136,3778673,3778242,3778019,3778668,3778325,3778136,3778673,3778242,3778091,3778668,3778325,3778136,3778673,3778466,3778091,3778668,3778541,3778136,3778673,3778466,3778091,3778668,3778541,3778136,3778673,3778466,3778091,3778668,3778565,3778136,3778673,3778466,3778099,3778668,3778565,3778136,3778673,3778466,3778099,3778868,3778645,3778136,3778673,3778514,3778099,3778868,3778645,3778136,3778673,3778514,3778099,3778868,3778693,3778136,3778673,3778514,3778107,3778868,3778693,3778136,3778673,3778514,3778107,3778868,3778709,3778136,3778673,3778514,3778107,3778868,3778709,3778136,3778673,3778786,3778107,3778868,3779021,3778136,3778673,3778786,3778115,3778868,3779021,3778136,3778673,3778786,3778115,3778988,3778136,3778673,3778786,3778115,3778988,3778136,3778673,3778786,3778115,3778988,3778144,3778673,3778988,3778144,3778673,3778988,3778144,3778673,3778988,3778144,3778673,3778988,3778144,3778673,3778988,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778673,3778673,3778673,3778673,3778673,3778673,3778673,3778673</t>
+          <t>3778136,3778019,3778242,3778019,3778668,3778253,3778542,3778136,3778019,3778242,3778019,3778668,3778253,3778136,3778019,3778242,3778019,3778668,3778325,3778136,3778091,3778242,3778091,3778668,3778325,3778136,3778091,3778466,3778091,3778668,3778541,3778136,3778091,3778466,3778091,3778668,3778541,3778136,3778091,3778466,3778091,3778668,3778565,3778136,3778099,3778466,3778099,3778668,3778565,3778136,3778099,3778466,3778099,3778868,3778645,3778136,3778099,3778514,3778099,3778868,3778645,3778136,3778099,3778514,3778099,3778868,3778693,3778136,3778107,3778514,3778107,3778868,3778693,3778136,3778107,3778514,3778107,3778868,3778709,3778136,3778107,3778514,3778107,3778868,3778709,3778136,3778107,3778786,3778107,3778868,3779021,3778136,3778115,3778786,3778115,3778868,3779021,3778136,3778115,3778786,3778115,3778988,3778136,3778115,3778786,3778115,3778988,3778136,3778115,3778786,3778115,3778988,3778144,3778673,3778988,3778144,3778673,3778988,3778144,3778673,3778988,3778144,3778673,3778988,3778144,3778673,3778988,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778144,3778673,3778673,3778673,3778673,3778673,3778673,3778673,3778673,3778673</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L17 W20/25; N=161; EHP=20585.000000; air:2x3,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x19,normal:18x18,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x45,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L17 W20/25; N=161; EHP=51726.861603; air:2x6,air:11x8,air:12x8,air:13x8,air:14x8,elite:67x1,fast:30x4,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x19,normal:18x18,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10018111,10018122,10018113,10048630,10018121,10018114,10018111,10018122,10018113,10048630,10018121,10018114,10018111,10018122,10018113,10048630,10018121,10018115,10018111,10018122,10018113,10048630,10018121,10018115,10018111,10018122,10018113,10018108,10018121,10018118,10018111,10018122,10018116,10018108,10018121,10018118,10018111,10018122,10018116,10018108,10018121,10018119,10018111,10018122,10018116,10018108,10018121,10018119,10018111,10018122,10018116,10048631,10018126,10018120,10018111,10018122,10018116,10048631,10018126,10018120,10018111,10018122,10018117,10048631,10018126,10018123,10018111,10018122,10018117,10048631,10018126,10018123,10018111,10018122,10018117,10018109,10018126,10018124,10018111,10018122,10018117,10018109,10018126,10018124,10018111,10018122,10018117,10018109,10018126,10045194,10018111,10018122,10018125,10018109,10018126,10045194,10018111,10018122,10018125,10018110,10018126,10018111,10018122,10018125,10018110,10018127,10018111,10018122,10018125,10018110,10018127,10018111,10018122,10018125,10018110,10018127,10018112,10018122,10018127,10018112,10018122,10018127,10018112,10018122,10018127,10018112,10018122,10018127,10018112,10018122,10018127,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018122,10018122,10018122,10018122,10018122,10018122</t>
+          <t>10018111,10048630,10018113,10048630,10018121,10018114,10018111,10048630,10018113,10048630,10018121,10018114,10018111,10048630,10018113,10048630,10018121,10018115,10018111,10048630,10018113,10048630,10018121,10018115,10018111,10018108,10018113,10018108,10018121,10018118,10018111,10018108,10018116,10018108,10018121,10018118,10018111,10018108,10018116,10018108,10018121,10018119,10018111,10018108,10018116,10018108,10018121,10018119,10018111,10048631,10018116,10048631,10018126,10018120,10018111,10048631,10018116,10048631,10018126,10018120,10018111,10048631,10018117,10048631,10018126,10018123,10018111,10048631,10018117,10048631,10018126,10018123,10018111,10018109,10018117,10018109,10018126,10018124,10018111,10018109,10018117,10018109,10018126,10018124,10018111,10018109,10018117,10018109,10018126,10045194,10018111,10018109,10018125,10018109,10018126,10045194,10018111,10018110,10018125,10018110,10018126,10018111,10018110,10018125,10018110,10018127,10018111,10018110,10018125,10018110,10018127,10018111,10018110,10018125,10018110,10018127,10018112,10018122,10018127,10018112,10018122,10018127,10018112,10018122,10018127,10018112,10018122,10018127,10018112,10018122,10018127,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018112,10018122,10018122,10018122,10018122,10018122,10018122,10018122</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L17 W21/25; N=167; EHP=20997.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x46,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x8,heavy:127x2</t>
+          <t>L17 W21/25; N=167; EHP=52786.060988; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x9,medium:123x8,normal:17x20,normal:18x20,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10018131,10018141,10018133,10048632,10018140,10018134,10018131,10018141,10018133,10048632,10018140,10018134,10018131,10018141,10018133,10048632,10018140,10018135,10018131,10018141,10018133,10048632,10018140,10018135,10018131,10018141,10018133,10018128,10018140,10018138,10018131,10018141,10018136,10018128,10018140,10018138,10018131,10018141,10018136,10018128,10018140,10018138,10018131,10018141,10018136,10018128,10018140,10045195,10018131,10018141,10018136,10048633,10018140,10045195,10018131,10018141,10018136,10048633,10018145,10018139,10018131,10018141,10018137,10048633,10018145,10018139,10018131,10018141,10018137,10048633,10018145,10018142,10018131,10018141,10018137,10018129,10018145,10018142,10018131,10018141,10018137,10018129,10018145,10018143,10018131,10018141,10018137,10018129,10018145,10018143,10018131,10018141,10018144,10018129,10018145,10018147,10018131,10018141,10018144,10018130,10018145,10018147,10018131,10018141,10018144,10018130,10018146,10018131,10018141,10018144,10018130,10018146,10018131,10018141,10018144,10018130,10018146,10018131,10018141,10018130,10018146,10018132,10018141,10018146,10018132,10018141,10018146,10018132,10018141,10018146,10018132,10018141,10018146,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018141,10018141,10018141,10018141,10018141,10018141</t>
+          <t>10018131,10048632,10018133,10048632,10018140,10018134,10018131,10048632,10018133,10048632,10018140,10018134,10018131,10048632,10018133,10048632,10018140,10018135,10018131,10048632,10018133,10048632,10018140,10018135,10018131,10018128,10018133,10018128,10018140,10018138,10018131,10018128,10018136,10018128,10018140,10018138,10018131,10018128,10018136,10018128,10018140,10018138,10018131,10018128,10018136,10018128,10018140,10045195,10018131,10048633,10018136,10048633,10018140,10045195,10018131,10048633,10018136,10048633,10018145,10018139,10018131,10048633,10018137,10048633,10018145,10018139,10018131,10048633,10018137,10048633,10018145,10018142,10018131,10018129,10018137,10018129,10018145,10018142,10018131,10018129,10018137,10018129,10018145,10018143,10018131,10018129,10018137,10018129,10018145,10018143,10018131,10018129,10018144,10018129,10018145,10018147,10018131,10018130,10018144,10018130,10018145,10018147,10018131,10018130,10018144,10018130,10018146,10018131,10018130,10018144,10018130,10018146,10018131,10018130,10018144,10018130,10018146,10018131,10018130,10018130,10018146,10018132,10018141,10018146,10018132,10018141,10018146,10018132,10018141,10018146,10018132,10018141,10018146,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018132,10018141,10018141,10018141,10018141,10018141,10018141,10018141</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L17 W22/25; N=173; EHP=21417.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x5,normal:17x21,normal:18x21,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x3,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x48,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L17 W22/25; N=173; EHP=53851.257070; air:2x8,air:11x8,air:12x8,air:13x8,air:14x10,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x8,medium:123x8,normal:17x21,normal:18x21,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10018151,10018161,10018153,10048634,10018160,10018154,10018151,10018161,10018153,10048634,10018160,10018154,10018151,10018161,10018153,10048634,10018160,10018155,10018151,10018161,10018153,10048634,10018160,10018155,10018151,10018161,10018153,10018148,10018160,10045196,10018151,10018161,10018153,10018148,10018160,10045196,10018151,10018161,10018156,10018148,10018160,10018158,10018151,10018161,10018156,10018148,10018160,10018158,10018151,10018161,10018156,10048635,10018165,10018159,10018151,10018161,10018156,10048635,10018165,10018159,10018151,10018161,10018156,10048635,10018165,10018162,10018151,10018161,10018157,10048635,10018165,10018162,10018151,10018161,10018157,10048635,10018165,10018163,10018151,10018161,10018157,10018149,10018165,10018163,10018151,10018161,10018157,10018149,10018165,10018163,10018151,10018161,10018157,10018149,10018165,10018167,10018151,10018161,10018164,10018149,10018165,10018167,10018151,10018161,10018164,10018150,10018166,10018151,10018161,10018164,10018150,10018166,10018151,10018161,10018164,10018150,10018166,10018151,10018161,10018164,10018150,10018166,10018151,10018161,10018166,10018152,10018161,10018166,10018152,10018161,10018166,10018152,10018161,10018166,10018152,10018161,10018166,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018161,10018161,10018161,10018161,10018161,10018161</t>
+          <t>10018151,10048634,10018153,10048634,10018160,10018154,10018151,10048634,10018153,10048634,10018160,10018154,10018151,10048634,10018153,10048634,10018160,10018155,10018151,10048634,10018153,10048634,10018160,10018155,10018151,10018148,10018153,10018148,10018160,10045196,10018151,10018148,10018153,10018148,10018160,10045196,10018151,10018148,10018156,10018148,10018160,10018158,10018151,10018148,10018156,10018148,10018160,10018158,10018151,10048635,10018156,10048635,10018165,10018159,10018151,10048635,10018156,10048635,10018165,10018159,10018151,10048635,10018156,10048635,10018165,10018162,10018151,10048635,10018157,10048635,10018165,10018162,10018151,10048635,10018157,10048635,10018165,10018163,10018151,10018149,10018157,10018149,10018165,10018163,10018151,10018149,10018157,10018149,10018165,10018163,10018151,10018149,10018157,10018149,10018165,10018167,10018151,10018149,10018164,10018149,10018165,10018167,10018151,10018150,10018164,10018150,10018166,10018151,10018150,10018164,10018150,10018166,10018151,10018150,10018164,10018150,10018166,10018151,10018150,10018164,10018150,10018166,10018151,10018161,10018166,10018152,10018161,10018166,10018152,10018161,10018166,10018152,10018161,10018166,10018152,10018161,10018166,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018152,10018161,10018161,10018161,10018161,10018161,10018161,10018161</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L17 W23/25; N=179; EHP=21846.000000; air:2x4,air:11x4,air:12x5,air:13x4,air:14x4,normal:17x22,normal:18x22,fast:30x6,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x50,heavy:86x2,heavy:88x3,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L17 W23/25; N=179; EHP=54909.904428; air:2x8,air:11x8,air:12x10,air:13x8,air:14x8,fast:30x6,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x8,medium:108x9,medium:123x9,normal:17x22,normal:18x22,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10018171,10018182,10018173,10048636,10018181,10018174,10018171,10018182,10018173,10048636,10018181,10018174,10018171,10018182,10018173,10048636,10018181,10018175,10018171,10018182,10018173,10048636,10018181,10018175,10018171,10018182,10018173,10048636,10018181,10018178,10018171,10018182,10018176,10018168,10018181,10018178,10018171,10018182,10018176,10018168,10018181,10018179,10018171,10018182,10018176,10018168,10018181,10018179,10018171,10018182,10018176,10018168,10018181,10018180,10018171,10018182,10018176,10048637,10018186,10018180,10018171,10018182,10018176,10048637,10018186,10018180,10018171,10018182,10018177,10048637,10018186,10018183,10018171,10018182,10018177,10048637,10018186,10018183,10018171,10018182,10018177,10018169,10018186,10018183,10018171,10018182,10018177,10018169,10018186,10018184,10018171,10018182,10018177,10018169,10018186,10018184,10018171,10018182,10018185,10018169,10018186,10018188,10018171,10018182,10018185,10018169,10018186,10018188,10018171,10018182,10018185,10018170,10018187,10018171,10018182,10018185,10018170,10018187,10018171,10018182,10018185,10018170,10018187,10018171,10018182,10018185,10018170,10018187,10018171,10018182,10018187,10018172,10018182,10018187,10018172,10018182,10018187,10018172,10018182,10018187,10018172,10018182,10018187,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018182,10018182,10018182,10018182,10018182,10018182</t>
+          <t>10018171,10048636,10018173,10048636,10018181,10018174,10018171,10048636,10018173,10048636,10018181,10018174,10018171,10048636,10018173,10048636,10018181,10018175,10018171,10048636,10018173,10048636,10018181,10018175,10018171,10048636,10018173,10048636,10018181,10018178,10018171,10018168,10018176,10018168,10018181,10018178,10018171,10018168,10018176,10018168,10018181,10018179,10018171,10018168,10018176,10018168,10018181,10018179,10018171,10018168,10018176,10018168,10018181,10018180,10018171,10048637,10018176,10048637,10018186,10018180,10018171,10048637,10018176,10048637,10018186,10018180,10018171,10048637,10018177,10048637,10018186,10018183,10018171,10048637,10018177,10048637,10018186,10018183,10018171,10018169,10018177,10018169,10018186,10018183,10018171,10018169,10018177,10018169,10018186,10018184,10018171,10018169,10018177,10018169,10018186,10018184,10018171,10018169,10018185,10018169,10018186,10018188,10018171,10018169,10018185,10018169,10018186,10018188,10018171,10018170,10018185,10018170,10018187,10018171,10018170,10018185,10018170,10018187,10018171,10018170,10018185,10018170,10018187,10018171,10018170,10018185,10018170,10018187,10018171,10018182,10018187,10018172,10018182,10018187,10018172,10018182,10018187,10018172,10018182,10018187,10018172,10018182,10018187,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018172,10018182,10018182,10018182,10018182,10018182,10018182,10018182</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L17 W24/25; N=185; EHP=23393.000000; air:2x5,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x23,normal:18x22,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x3,medium:83x9,swarm:84x51,heavy:86x3,heavy:88x2,fast:98x6,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L17 W24/25; N=185; EHP=58805.065232; air:2x10,air:11x8,air:12x8,air:13x10,air:14x8,fast:30x5,fast:58x6,fast:64x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x3,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x23,normal:18x22,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10018192,10018203,10018194,10048638,10018202,10018195,10018210,10018192,10018203,10018194,10048638,10018202,10018195,10018192,10018203,10018194,10048638,10018202,10018195,10018192,10018203,10018194,10048638,10018202,10018196,10018192,10018203,10018194,10018189,10018202,10018196,10018192,10018203,10018197,10018189,10018202,10018196,10018192,10018203,10018197,10018189,10018202,10018199,10018192,10018203,10018197,10018189,10018202,10018199,10018192,10018203,10018197,10018189,10018202,10018200,10018192,10018203,10018197,10048639,10018202,10018200,10018192,10018203,10018197,10048639,10018207,10018201,10018192,10018203,10018198,10048639,10018207,10018201,10018192,10018203,10018198,10048639,10018207,10018204,10018192,10018203,10018198,10018190,10018207,10018204,10018192,10018203,10018198,10018190,10018207,10018204,10018192,10018203,10018198,10018190,10018207,10018205,10018192,10018203,10018198,10018190,10018207,10018205,10018192,10018203,10018206,10018190,10018207,10018209,10018192,10018203,10018206,10018191,10018207,10018209,10018192,10018203,10018206,10018191,10018208,10018192,10018203,10018206,10018191,10018208,10018192,10018203,10018206,10018191,10018208,10018193,10018203,10018191,10018208,10018193,10018203,10018208,10018193,10018203,10018208,10018193,10018203,10018208,10018193,10018203,10018208,10018193,10018203,10018208,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018203,10018203,10018203,10018203,10018203,10018203,10018203,10018203</t>
+          <t>10018192,10048638,10018194,10048638,10018202,10018195,10018210,10018192,10048638,10018194,10048638,10018202,10018195,10018192,10048638,10018194,10048638,10018202,10018195,10018192,10048638,10018194,10048638,10018202,10018196,10018192,10018189,10018194,10018189,10018202,10018196,10018192,10018189,10018197,10018189,10018202,10018196,10018192,10018189,10018197,10018189,10018202,10018199,10018192,10018189,10018197,10018189,10018202,10018199,10018192,10018189,10018197,10018189,10018202,10018200,10018192,10048639,10018197,10048639,10018202,10018200,10018192,10048639,10018197,10048639,10018207,10018201,10018192,10048639,10018198,10048639,10018207,10018201,10018192,10048639,10018198,10048639,10018207,10018204,10018192,10018190,10018198,10018190,10018207,10018204,10018192,10018190,10018198,10018190,10018207,10018204,10018192,10018190,10018198,10018190,10018207,10018205,10018192,10018190,10018198,10018190,10018207,10018205,10018192,10018190,10018206,10018190,10018207,10018209,10018192,10018191,10018206,10018191,10018207,10018209,10018192,10018191,10018206,10018191,10018208,10018192,10018191,10018206,10018191,10018208,10018192,10018191,10018206,10018191,10018208,10018193,10018191,10018191,10018208,10018193,10018203,10018208,10018193,10018203,10018208,10018193,10018203,10018208,10018193,10018203,10018208,10018193,10018203,10018208,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018193,10018203,10018203,10018203,10018203,10018203,10018203,10018203,10018203,10018203</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L17 W25/25; N=191; EHP=46691.000000; air:2x4,air:11x5,air:12x4,air:13x5,air:14x5,normal:17x22,normal:18x23,fast:30x5,heavy:31x3,heavy:40x3,fast:58x6,fast:64x6,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x10,swarm:84x53,heavy:86x3,heavy:88x2,fast:98x5,medium:108x9,medium:123x9,heavy:127x2,boss:132x1</t>
+          <t>L17 W25/25; N=191; EHP=117358.811068; air:2x8,air:11x10,air:12x8,air:13x10,air:14x10,boss:132x1,fast:30x5,fast:58x6,fast:64x6,fast:98x5,heavy:31x3,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x10,medium:108x9,medium:123x9,normal:17x22,normal:18x23,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L17/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L17/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>248</v>
+        <v>370</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>241</v>
+        <v>330</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>234</v>
+        <v>290</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>227</v>
+        <v>360</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>213</v>
+        <v>300</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>199</v>
+        <v>310</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>192</v>
+        <v>280</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>185</v>
+        <v>370</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>178</v>
+        <v>280</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>171</v>
+        <v>310</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>164</v>
+        <v>280</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>143</v>
+        <v>280</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>136</v>
+        <v>370</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>129</v>
+        <v>270</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>300</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>260</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>300</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>370</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>185</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
